--- a/20-06-26/Furqan.xlsx
+++ b/20-06-26/Furqan.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B029E51-0949-4142-B1CD-4DDBF8AB3294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966771E8-CFFB-4514-BC1B-AC35F48A0477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3351,7 +3351,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3379,7 +3379,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4572,7 +4572,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4600,7 +4600,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5793,7 +5793,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5821,7 +5821,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7014,7 +7014,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7042,7 +7042,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8235,7 +8235,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8263,7 +8263,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9456,7 +9456,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9484,7 +9484,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10674,7 +10674,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10702,7 +10702,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11891,7 +11891,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11919,7 +11919,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13108,7 +13108,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13136,7 +13136,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14325,7 +14325,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14353,7 +14353,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18292,7 +18292,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18320,7 +18320,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19509,7 +19509,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19537,7 +19537,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20726,7 +20726,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20754,7 +20754,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21943,7 +21943,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21971,7 +21971,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23165,7 +23165,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23193,7 +23193,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23404,7 +23404,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>2354.4435524999999</v>
+        <v>0</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23490,15 +23490,15 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>7082.4375</v>
+        <v>1311.5625</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K16" s="172">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23506,23 +23506,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>566.59500000000003</v>
+        <v>104.925</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>6515.8424999999997</v>
+        <v>1206.6375</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>1289.3183999999999</v>
+        <v>277.00200000000001</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>73.575508499999998</v>
+        <v>7.4181974999999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>7878.7364084999999</v>
+        <v>1491.0576974999999</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'4'!P35</f>
-        <v>45977.121136199989</v>
+        <v>0</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23564,15 +23564,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>6820.125</v>
+        <v>524.625</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23580,23 +23580,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>545.61</v>
+        <v>41.97</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>6274.5150000000003</v>
+        <v>482.65499999999997</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>1216.9201499999999</v>
+        <v>117.72585000000001</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>37.457175750000005</v>
+        <v>3.0019042499999999</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>7528.8923257500001</v>
+        <v>603.38275425000006</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23638,15 +23638,15 @@
       <c r="G18" s="114"/>
       <c r="H18" s="172">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18</f>
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>8131.6875</v>
+        <v>1311.5625</v>
       </c>
       <c r="J18" s="172">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K18" s="172">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -23654,23 +23654,23 @@
       </c>
       <c r="L18" s="175">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>650.53499999999997</v>
+        <v>104.925</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="2"/>
-        <v>7481.1525000000001</v>
+        <v>1206.6375</v>
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>1463.0741999999998</v>
+        <v>277.00200000000001</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>56.111791500000002</v>
+        <v>7.4181974999999998</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>9000.3384914999988</v>
+        <v>1491.0576974999999</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23708,15 +23708,15 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>8716.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
@@ -23724,23 +23724,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>697.34399999999994</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>8019.4559999999992</v>
+        <v>0</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1521.9532799999997</v>
+        <v>0</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>47.707046400000003</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>9589.1163264000006</v>
+        <v>0</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23778,15 +23778,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23794,23 +23794,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>5346.3040000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1014.6355199999999</v>
+        <v>0</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>31.804697600000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>6392.7442175999995</v>
+        <v>0</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23848,15 +23848,15 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -23864,23 +23864,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>5346.3040000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1040.78592</v>
+        <v>0</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>31.935449600000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>6419.0253696</v>
+        <v>0</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23918,11 +23918,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>4707.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -23930,27 +23930,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>164.76600000000002</v>
+        <v>0</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>4307.4540000000006</v>
+        <v>0</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>775.34172000000012</v>
+        <v>0</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>25.413978600000007</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>5108.2096986000006</v>
+        <v>0</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24108,7 +24108,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>20.5</v>
+        <v>1.5</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24119,39 +24119,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>820</v>
+        <v>60</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>47081.049999999996</v>
+        <v>3147.75</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>164.76600000000002</v>
+        <v>0</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>3625.2560000000003</v>
+        <v>251.82</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>43291.028000000006</v>
+        <v>2895.9300000000003</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>8322.0291899999993</v>
+        <v>671.72984999999994</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>304.00564795000003</v>
+        <v>17.838299249999999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>51917.062837949998</v>
+        <v>3585.4981492499996</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>51917.062837949983</v>
+        <v>3585.4981492500001</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24314,7 +24314,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>47081.049999999996</v>
+        <v>3147.75</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24335,7 +24335,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>3625.2560000000003</v>
+        <v>251.82</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24356,7 +24356,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>164.76600000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24378,7 +24378,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>43291.027999999991</v>
+        <v>2895.93</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>8322.0291899999993</v>
+        <v>671.72984999999994</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24425,7 +24425,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>51613.057189999992</v>
+        <v>3567.65985</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>1290.32642975</v>
+        <v>89.19149625</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24460,7 +24460,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>52903.383619749991</v>
+        <v>3656.85134625</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24540,7 +24540,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
@@ -24632,7 +24632,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24660,7 +24660,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24954,39 +24954,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>30</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>1573.875</v>
-      </c>
-      <c r="J16" s="103">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103"/>
       <c r="K16" s="104">
         <f>I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>125.91</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1447.9649999999999</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>279.52019999999999</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>43.187129999999996</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>1770.6723299999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -25078,12 +25074,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>10</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="3"/>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J18" s="117"/>
       <c r="K18" s="1">
@@ -25092,23 +25086,23 @@
       </c>
       <c r="L18" s="105">
         <f t="shared" si="5"/>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="6"/>
-        <v>482.65499999999997</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>86.877899999999997</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="1"/>
-        <v>14.238322499999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="2"/>
-        <v>583.77122249999991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25462,11 +25456,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -25475,23 +25469,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>167.88</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>366.3981</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>57.425452499999992</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2354.4435524999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25541,7 +25535,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25562,7 +25556,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>167.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25605,7 +25599,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25630,7 +25624,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>366.3981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25652,7 +25646,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2297.0180999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25677,7 +25671,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>57.425452499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25687,7 +25681,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2354.4435524999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25767,7 +25761,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -25859,7 +25853,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25887,7 +25881,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26998,7 +26992,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -27090,7 +27084,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27118,7 +27112,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28225,7 +28219,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -28316,7 +28310,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28344,7 +28338,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28638,39 +28632,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>80</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>4197</v>
-      </c>
-      <c r="J16" s="103">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103"/>
       <c r="K16" s="104">
         <f>I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>335.76</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>3861.24</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>732.7962</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>22.970180999999997</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>4617.0063809999992</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -28702,39 +28692,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>120</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>6295.5</v>
-      </c>
-      <c r="J17" s="117">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>503.64</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>5791.86</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>1099.1942999999999</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>34.455271500000002</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>6925.5095714999998</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -28766,39 +28752,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>120</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>6295.5</v>
-      </c>
-      <c r="J18" s="117">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="117"/>
       <c r="K18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>503.64</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>5791.86</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>1099.1942999999999</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>34.455271500000002</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>6925.5095714999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28826,39 +28808,35 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>120</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>8716.7999999999993</v>
-      </c>
-      <c r="J19" s="117">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="117"/>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>697.34399999999994</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>8019.4559999999992</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>1521.9532799999997</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>47.707046400000003</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>9589.1163264000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28886,39 +28864,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>80</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>5811.2</v>
-      </c>
-      <c r="J20" s="117">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>5346.3040000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>1014.6355199999999</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>31.804697600000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>6392.7442175999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28946,39 +28920,35 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>80</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>5811.2</v>
-      </c>
-      <c r="J21" s="117">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="117"/>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>5346.3040000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>1040.78592</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>31.935449600000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>6419.0253696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29006,37 +28976,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>120</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>4707.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>164.76600000000002</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>4307.4540000000006</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>775.34172000000012</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>25.413978600000007</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>5108.2096986000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29166,36 +29134,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>41834.799999999996</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>164.76600000000002</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>3205.5560000000005</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>38464.477999999996</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>7283.9012400000001</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>228.74189620000001</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>45977.121136199996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29245,7 +29213,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>41834.799999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29266,7 +29234,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>3205.5560000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29287,7 +29255,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>164.76600000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29309,7 +29277,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>38464.477999999988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29334,7 +29302,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>7283.9012400000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29356,7 +29324,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>45748.379239999987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29381,7 +29349,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>228.74189619999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29391,7 +29359,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>45977.121136199989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29471,7 +29439,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -29563,7 +29531,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29591,7 +29559,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30784,7 +30752,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30812,7 +30780,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
